--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487733_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487733_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7542</v>
+        <v>0.5817</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1005</v>
+        <v>-0.0004</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8547</v>
+        <v>0.5821</v>
       </c>
       <c r="G2" t="n">
         <v>0.282</v>
@@ -610,13 +610,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4722</v>
+        <v>0.2997</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5933</v>
+        <v>0.3208</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3736</v>
+        <v>0.3191</v>
       </c>
       <c r="E3" t="n">
         <v>-0.2017</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5752</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0434</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2427</v>
+        <v>-0.2972</v>
       </c>
       <c r="T3" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0004</v>
+        <v>-0.055</v>
       </c>
       <c r="V3" t="n">
         <v>0.6597</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1687</v>
+        <v>0.3048</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2996</v>
+        <v>0.198</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4683</v>
+        <v>0.1069</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2295</v>
+        <v>1.1007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5652</v>
+        <v>0.5841</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7947</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5899</v>
+        <v>1.3521</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6838</v>
+        <v>0.6797</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0939</v>
+        <v>0.6724</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8194</v>
+        <v>-0.2513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1187</v>
+        <v>-0.0956</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7008</v>
+        <v>-0.1557</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3273</v>
+        <v>-0.2854</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.544</v>
+        <v>-0.466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2167</v>
+        <v>0.1806</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1224</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2224</v>
+        <v>-0.0224</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0022</v>
+        <v>-0.4815</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2202</v>
+        <v>0.4591</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1007</v>
+        <v>-0.7675</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5841</v>
+        <v>-0.3732</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5165999999999999</v>
+        <v>-0.3943</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3521</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6797</v>
+        <v>0.0618</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6724</v>
+        <v>0.0228</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2513</v>
+        <v>-0.8521</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0956</v>
+        <v>-0.435</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1557</v>
+        <v>-0.4171</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8127</v>
+        <v>-0.7489</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6662</v>
+        <v>-0.5661</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1465</v>
+        <v>-0.1828</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1224</v>
+        <v>0.3299</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4045</v>
+        <v>0.3299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2315</v>
+        <v>-0.3055</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5816</v>
+        <v>-0.0007</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3501</v>
+        <v>-0.3048</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7675</v>
+        <v>-0.2295</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3732</v>
+        <v>0.5652</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3943</v>
+        <v>-0.7947</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.5899</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0618</v>
+        <v>0.6838</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0228</v>
+        <v>-0.0939</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8521</v>
+        <v>-0.8194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.435</v>
+        <v>-0.1187</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4171</v>
+        <v>-0.7008</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.958</v>
+        <v>-0.464</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6662</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2918</v>
+        <v>0.3802</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3299</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3299</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>J. MUNRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2323</v>
+        <v>-2.3066</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6551</v>
+        <v>-0.9666</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5772</v>
+        <v>-1.3399</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.1239</v>
+        <v>0.8087</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.003</v>
+        <v>1.1452</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.1209</v>
+        <v>-0.3364</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.7412</v>
+        <v>3.7249</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.866</v>
+        <v>1.8702</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8752</v>
+        <v>1.8547</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3827</v>
+        <v>-2.9162</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.137</v>
+        <v>-0.725</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2458</v>
+        <v>-2.1912</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4917</v>
+        <v>-0.3824</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7907</v>
+        <v>-0.8109</v>
       </c>
       <c r="U7" t="n">
-        <v>0.701</v>
+        <v>0.4285</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4</v>
+        <v>-0.4045</v>
       </c>
       <c r="W7" t="n">
-        <v>4.2358</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8358</v>
+        <v>-0.4045</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MUNRO</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4344</v>
+        <v>-3.5058</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.367</v>
+        <v>-1.6561</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.0674</v>
+        <v>-1.8497</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8087</v>
+        <v>-6.1239</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1452</v>
+        <v>-3.003</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3364</v>
+        <v>-3.1209</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7249</v>
+        <v>-3.7412</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8702</v>
+        <v>-1.866</v>
       </c>
       <c r="L8" t="n">
-        <v>1.8547</v>
+        <v>-1.8752</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9162</v>
+        <v>-2.3827</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.725</v>
+        <v>-1.137</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1912</v>
+        <v>-1.2458</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3284</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.8806</v>
+        <v>-1.9403</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5523</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5103</v>
+        <v>0.2181</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2113</v>
+        <v>-0.2103</v>
       </c>
       <c r="U8" t="n">
-        <v>0.701</v>
+        <v>0.4285</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4045</v>
+        <v>2.4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>4.2358</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.4045</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0065</v>
+        <v>-3.5605</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6441</v>
+        <v>-2.1436</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3624</v>
+        <v>-1.4169</v>
       </c>
       <c r="G9" t="n">
         <v>-3.7681</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.522</v>
+        <v>-0.076</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0296</v>
+        <v>-0.5291</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5077</v>
+        <v>0.4531</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6866</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2227</v>
+        <v>-4.1732</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4463</v>
+        <v>-3.0455</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7764</v>
+        <v>-1.1277</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1942</v>
+        <v>-4.9708</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0618</v>
+        <v>-1.7169</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1324</v>
+        <v>-3.2538</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4256</v>
+        <v>-3.4291</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0453</v>
+        <v>-1.5489</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3803</v>
+        <v>-1.8802</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6198</v>
+        <v>-1.5417</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1071</v>
+        <v>-0.1681</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5127</v>
+        <v>-1.3737</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.1344</v>
+        <v>1.3582</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3939</v>
+        <v>0.2215</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3017</v>
+        <v>-0.1806</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6956</v>
+        <v>0.4021</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.288</v>
+        <v>-0.7821</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6597</v>
+        <v>0.5642</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6283</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.473</v>
+        <v>-4.1954</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0455</v>
+        <v>-2.4463</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4275</v>
+        <v>-1.7491</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9708</v>
+        <v>-0.1942</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7169</v>
+        <v>-0.0618</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2538</v>
+        <v>-0.1324</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.4291</v>
+        <v>1.4256</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5489</v>
+        <v>0.0453</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8802</v>
+        <v>1.3803</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5417</v>
+        <v>-1.6198</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1681</v>
+        <v>-0.1071</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3737</v>
+        <v>-1.5127</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3582</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.4212</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1806</v>
+        <v>-0.3017</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1023</v>
+        <v>0.7229</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7821</v>
+        <v>-2.288</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3463</v>
+        <v>-1.6283</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.8637</v>
+        <v>-16.8638</v>
       </c>
       <c r="E12" t="n">
         <v>-10.7444</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.119400000000001</v>
+        <v>-6.1193</v>
       </c>
       <c r="G12" t="n">
         <v>-13.906</v>
@@ -1366,7 +1366,7 @@
         <v>-1.5464</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3789000000000002</v>
+        <v>-0.3789000000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-1.1675</v>
@@ -1390,7 +1390,7 @@
         <v>9.701599999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0935</v>
+        <v>-1.0934</v>
       </c>
       <c r="T12" t="n">
         <v>-4.1723</v>
@@ -1402,10 +1402,10 @@
         <v>-0.8939999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>5.6463</v>
+        <v>5.646299999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.5403</v>
+        <v>-6.540300000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4624</v>
+        <v>6.89</v>
       </c>
       <c r="E13" t="n">
-        <v>5.7952</v>
+        <v>6.1956</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6672</v>
+        <v>0.6945</v>
       </c>
       <c r="G13" t="n">
         <v>4.8507</v>
@@ -1468,13 +1468,13 @@
         <v>0.3881</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6122</v>
+        <v>-0.1845</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6662</v>
+        <v>-0.2658</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0541</v>
+        <v>0.0813</v>
       </c>
       <c r="V13" t="n">
         <v>1.8358</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3388</v>
+        <v>3.9929</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9329</v>
+        <v>2.5325</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4059</v>
+        <v>1.4604</v>
       </c>
       <c r="G14" t="n">
         <v>3.477</v>
@@ -1546,13 +1546,13 @@
         <v>1.3582</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4737</v>
+        <v>0.1278</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3656</v>
+        <v>-0.0348</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1081</v>
+        <v>0.1626</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0556</v>
+        <v>3.9917</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3595</v>
+        <v>3.1593</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6962</v>
+        <v>0.8324</v>
       </c>
       <c r="G15" t="n">
         <v>1.87</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0796</v>
+        <v>0.0157</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1806</v>
+        <v>-0.3808</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2602</v>
+        <v>0.3965</v>
       </c>
       <c r="V15" t="n">
         <v>0.9418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>O. MENDEZ BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7811</v>
+        <v>3.5909</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9802999999999999</v>
+        <v>1.8094</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8008</v>
+        <v>1.7815</v>
       </c>
       <c r="G16" t="n">
-        <v>2.394</v>
+        <v>0.9735</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1236</v>
+        <v>1.3973</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5175</v>
+        <v>-0.4237</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4043</v>
+        <v>0.8189</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5849</v>
+        <v>1.3594</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9892</v>
+        <v>-0.5405</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9897</v>
+        <v>0.1546</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4614</v>
+        <v>0.0379</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5283</v>
+        <v>0.1168</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6111</v>
+        <v>-0.0244</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.424</v>
+        <v>-0.4871</v>
       </c>
       <c r="U16" t="n">
-        <v>1.035</v>
+        <v>0.4627</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. MENDEZ BLANCO</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3179</v>
+        <v>3.3089</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5091</v>
+        <v>1.0804</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8088</v>
+        <v>2.2285</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9735</v>
+        <v>2.394</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3973</v>
+        <v>-0.1236</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4237</v>
+        <v>2.5175</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8189</v>
+        <v>1.4043</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3594</v>
+        <v>-0.5849</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5405</v>
+        <v>1.9892</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1546</v>
+        <v>0.9897</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0379</v>
+        <v>0.4614</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1168</v>
+        <v>0.5283</v>
       </c>
       <c r="P17" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2974</v>
+        <v>0.1388</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7874</v>
+        <v>-0.3239</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4899</v>
+        <v>0.4627</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2253</v>
+        <v>2.2489</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9676</v>
+        <v>0.8953</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2577</v>
+        <v>1.3536</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3484</v>
+        <v>1.7366</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4128</v>
+        <v>1.1444</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7611</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6662</v>
+        <v>1.4429</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5232</v>
+        <v>1.2399</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1894</v>
+        <v>0.203</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3179</v>
+        <v>0.2937</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1104</v>
+        <v>-0.0956</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4282</v>
+        <v>0.3893</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7463</v>
+        <v>0.9702</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S18" t="n">
-        <v>0.777</v>
+        <v>0.1063</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3656</v>
+        <v>-0.5476</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4114</v>
+        <v>0.6539</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8462</v>
+        <v>-0.5642</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8395</v>
+        <v>1.9339</v>
       </c>
       <c r="E19" t="n">
-        <v>0.595</v>
+        <v>0.5672</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2446</v>
+        <v>1.3668</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7366</v>
+        <v>2.3484</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1444</v>
+        <v>-0.4128</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5921999999999999</v>
+        <v>2.7611</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4429</v>
+        <v>2.6662</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2399</v>
+        <v>-0.5232</v>
       </c>
       <c r="L19" t="n">
-        <v>0.203</v>
+        <v>3.1894</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2937</v>
+        <v>-0.3179</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0956</v>
+        <v>0.1104</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3893</v>
+        <v>-0.4282</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9702</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3031</v>
+        <v>0.4856</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8479</v>
+        <v>-0.0348</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5204</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>0.8462</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2566</v>
+        <v>1.4568</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5754</v>
+        <v>-0.3752</v>
       </c>
       <c r="F20" t="n">
         <v>1.832</v>
@@ -2014,10 +2014,10 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0247</v>
+        <v>0.1755</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3634</v>
+        <v>-0.1632</v>
       </c>
       <c r="U20" t="n">
         <v>0.3387</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0428</v>
+        <v>-1.1731</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9548</v>
+        <v>-0.3399</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1836</v>
+        <v>1.7443</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5034</v>
+        <v>2.1503</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3197</v>
+        <v>-0.406</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4108</v>
+        <v>1.1168</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6138</v>
+        <v>1.6395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.203</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2271</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1104</v>
+        <v>0.5108</v>
       </c>
       <c r="O21" t="n">
         <v>0.1168</v>
       </c>
       <c r="P21" t="n">
-        <v>0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1707</v>
+        <v>0.3244</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4262</v>
+        <v>-0.0805</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2555</v>
+        <v>0.4049</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2239</v>
+        <v>-1.8836</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1096</v>
+        <v>-1.3798</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.44</v>
+        <v>-1.4553</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6697</v>
+        <v>0.0755</v>
       </c>
       <c r="G22" t="n">
-        <v>1.7443</v>
+        <v>-0.1836</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1503</v>
+        <v>-0.5034</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.406</v>
+        <v>0.3197</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1168</v>
+        <v>-0.4108</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6395</v>
+        <v>-0.6138</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.203</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.2271</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5108</v>
+        <v>0.1104</v>
       </c>
       <c r="O22" t="n">
         <v>0.1168</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3878</v>
+        <v>-0.1663</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1806</v>
+        <v>-0.0743</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5684</v>
+        <v>-0.092</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8836</v>
+        <v>-1.2239</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6716</v>
+        <v>-3.2984</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.2827</v>
+        <v>-4.8823</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6111</v>
+        <v>1.5839</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9709</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2245</v>
+        <v>0.1486</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8479</v>
+        <v>-0.4475</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6234</v>
+        <v>0.5961</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.5896</v>
+        <v>-4.6991</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7675</v>
+        <v>-3.0678</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8221</v>
+        <v>-1.6313</v>
       </c>
       <c r="G24" t="n">
         <v>-2.839</v>
@@ -2326,13 +2326,13 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0554</v>
+        <v>-0.0541</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0617</v>
+        <v>-0.2386</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0063</v>
+        <v>0.1845</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2239</v>
@@ -2365,13 +2365,13 @@
         <v>6.119200000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>10.7445</v>
+        <v>10.7446</v>
       </c>
       <c r="G25" t="n">
         <v>13.9062</v>
       </c>
       <c r="H25" t="n">
-        <v>3.089599999999999</v>
+        <v>3.0896</v>
       </c>
       <c r="I25" t="n">
         <v>10.8164</v>
@@ -2383,7 +2383,7 @@
         <v>2.7106</v>
       </c>
       <c r="L25" t="n">
-        <v>9.648999999999999</v>
+        <v>9.648999999999997</v>
       </c>
       <c r="M25" t="n">
         <v>1.5464</v>
@@ -2398,7 +2398,7 @@
         <v>0.9701999999999998</v>
       </c>
       <c r="Q25" t="n">
-        <v>-9.7018</v>
+        <v>-9.701799999999999</v>
       </c>
       <c r="R25" t="n">
         <v>10.6718</v>
@@ -2407,10 +2407,10 @@
         <v>1.0934</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.0789</v>
+        <v>-3.078899999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>4.172299999999999</v>
+        <v>4.1723</v>
       </c>
       <c r="V25" t="n">
         <v>0.8938000000000001</v>
